--- a/docs/asset-management/dialogue-voiceover-tracker.xlsx
+++ b/docs/asset-management/dialogue-voiceover-tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R9c0391c1b4d84296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active S1 + Shared" sheetId="2" r:id="R4abe9ceca703453c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2 Draft" sheetId="3" r:id="Rb3614283d68e40f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archived Dialogue" sheetId="4" r:id="R3bbbeed192d747a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="5" r:id="Rf05b2f5c26e4499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R3217cb2f7d624d3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active S1 + Shared" sheetId="2" r:id="Rb23a33dd15eb41c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2 Draft" sheetId="3" r:id="R2c3b85ab2fc44454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archived Dialogue" sheetId="4" r:id="R5af457ba26c6480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="5" r:id="Re7030c5b6d5b4fde"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -717,7 +717,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="28" t="str">
-        <x:v>Current baseline: PromptCraft v137 | Active S1 dialogue, planned S2 dialogue, and archived legacy lines</x:v>
+        <x:v>Current baseline: PROMPTCRAFT_V429 | Active S1/S2 dialogue, planned line recordings, and archived legacy wording</x:v>
       </x:c>
       <x:c r="B2" s="28"/>
       <x:c r="C2" s="28"/>
@@ -735,48 +735,42 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="35" t="str">
-        <x:v>Active S1/shared lines</x:v>
+        <x:v>Active structured dialogue</x:v>
       </x:c>
       <x:c r="B4" s="35" t="str">
-        <x:v>S2 draft lines</x:v>
+        <x:v>S2 active + intervention voice entries</x:v>
       </x:c>
       <x:c r="C4" s="35" t="str">
         <x:v>Archived lines</x:v>
       </x:c>
       <x:c r="D4" s="35" t="str">
-        <x:v>Professor Pixel lines</x:v>
+        <x:v>Professor Pixel structured lines</x:v>
       </x:c>
       <x:c r="E4" s="35" t="str">
-        <x:v>Jordan lines</x:v>
+        <x:v>Jordan active voice entries</x:v>
       </x:c>
       <x:c r="F4" s="35" t="str">
-        <x:v>Draft recordings</x:v>
+        <x:v>Current audio files</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="43" t="n">
-        <x:f>COUNTA('Active S1 + Shared'!A2:A200)</x:f>
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="43" t="n">
-        <x:f>COUNTA('S2 Draft'!A2:A200)</x:f>
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="43" t="n">
-        <x:f>COUNTA('Archived Dialogue'!A2:A200)</x:f>
         <x:v>38</x:v>
       </x:c>
       <x:c r="D5" s="43" t="n">
-        <x:f>COUNTIF('Active S1 + Shared'!B2:B200,"Professor Pixel")+COUNTIF('S2 Draft'!B2:B200,"Professor Pixel")+COUNTIF('Archived Dialogue'!B2:B200,"Professor Pixel")</x:f>
-        <x:v>112</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E5" s="43" t="n">
-        <x:f>COUNTIF('S2 Draft'!B2:B200,"Jordan")</x:f>
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F5" s="43" t="n">
-        <x:f>COUNTIF('S2 Draft'!K2:K200,"Draft")</x:f>
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -804,7 +798,7 @@
         <x:v>Active S1 + Shared</x:v>
       </x:c>
       <x:c r="B8" s="53" t="str">
-        <x:v>Current Professor Pixel dialogue still relevant to the clean-shell runtime.</x:v>
+        <x:v>Current Professor Pixel/shared lines and S1 dialogue used by the V429 runtime.</x:v>
       </x:c>
       <x:c r="C8" s="62"/>
       <x:c r="D8" s="62"/>
@@ -816,7 +810,7 @@
         <x:v>S2 Draft</x:v>
       </x:c>
       <x:c r="B9" s="53" t="str">
-        <x:v>New Pixel and Jordan lines for the redesigned S2 opening. These are not final recordings yet.</x:v>
+        <x:v>Current S2 opening/diagnosis wording plus the four Jordan intervention voice lines. Audio remains planned unless a file exists.</x:v>
       </x:c>
       <x:c r="C9" s="62"/>
       <x:c r="D9" s="62"/>
@@ -828,7 +822,7 @@
         <x:v>Archived Dialogue</x:v>
       </x:c>
       <x:c r="B10" s="53" t="str">
-        <x:v>Old S2–S8 lines preserved for reference but removed from the active runtime.</x:v>
+        <x:v>Old S2-S8 wording preserved for reference only; do not reconnect old mechanics from it.</x:v>
       </x:c>
       <x:c r="C10" s="62"/>
       <x:c r="D10" s="62"/>
@@ -845,7 +839,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="58" t="str">
-        <x:v>Important: S2 lines are drafts. Lock the diagnosis choices, feedback combinations, and opening pacing before recording them.</x:v>
+        <x:v>Source of truth: src/js/content/dialogue-data.js for structured dialogue and src/js/scenarios/s2-metacognition.js for Jordan intervention lines.</x:v>
       </x:c>
       <x:c r="B12" s="58"/>
       <x:c r="C12" s="58"/>
@@ -3643,7 +3637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdda7159d7e024067"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58a762690dbf4981"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3729,7 +3723,7 @@
         <x:v>neutral</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>Meet Jordan. He submits every assignment on time, earns passing grades, and appears to be keeping up with the course.</x:v>
+        <x:v>Meet Jordan. He completes his assignments, earns passing grades, and seems to be doing fine.</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
         <x:v>p86.mp3</x:v>
@@ -3738,28 +3732,28 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p86.mp3</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J2" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K2" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L2" s="14"/>
       <x:c r="M2" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N2" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 opening line.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="14" t="str">
-        <x:v>p87</x:v>
+        <x:v>jordan-s2-01</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>Professor Pixel</x:v>
+        <x:v>Jordan</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>Scenario 2</x:v>
@@ -3768,40 +3762,40 @@
         <x:v>scenarioStart_metacognition</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
-        <x:v>thinking</x:v>
+        <x:v>neutral</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>A better result sounds promising. But it does not necessarily mean Jordan understands what produced it.</x:v>
+        <x:v>I got an 84 on this assignment. That's better than last time, so I guess something worked.</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
-        <x:v>p87.mp3</x:v>
+        <x:v>jordan-s2-01.mp3</x:v>
       </x:c>
       <x:c r="H3" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p87.mp3</x:v>
+        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-01.mp3</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J3" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K3" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L3" s="14"/>
       <x:c r="M3" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N3" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 opening line.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="14" t="str">
-        <x:v>p88</x:v>
+        <x:v>jordan-s2-02</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>Professor Pixel</x:v>
+        <x:v>Jordan</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
         <x:v>Scenario 2</x:v>
@@ -3810,40 +3804,40 @@
         <x:v>scenarioStart_metacognition</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
-        <x:v>skeptical</x:v>
+        <x:v>uncertain</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>Jordan completed the work, so do not assume this is simply a motivation problem. Because his grade improved, the real problem is easy to overlook.</x:v>
+        <x:v>I reread the chapter a few times. Some parts eventually made more sense, but I couldn't tell you what actually helped.</x:v>
       </x:c>
       <x:c r="G4" s="14" t="str">
-        <x:v>p88.mp3</x:v>
+        <x:v>jordan-s2-02.mp3</x:v>
       </x:c>
       <x:c r="H4" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p88.mp3</x:v>
+        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-02.mp3</x:v>
       </x:c>
       <x:c r="I4" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J4" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K4" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L4" s="14"/>
       <x:c r="M4" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N4" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 opening line.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="14" t="str">
-        <x:v>p89</x:v>
+        <x:v>jordan-s2-03</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Professor Pixel</x:v>
+        <x:v>Jordan</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Scenario 2</x:v>
@@ -3852,37 +3846,37 @@
         <x:v>scenarioStart_metacognition</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>encouraging</x:v>
+        <x:v>frustrated</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>Listen to the evidence Jordan gave you. Choose the two instructional needs most clearly supported by his comments.</x:v>
+        <x:v>Next time I'll probably reread everything again and hope it works.</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>p89.mp3</x:v>
+        <x:v>jordan-s2-03.mp3</x:v>
       </x:c>
       <x:c r="H5" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p89.mp3</x:v>
+        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-03.mp3</x:v>
       </x:c>
       <x:c r="I5" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J5" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K5" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L5" s="14"/>
       <x:c r="M5" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N5" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 opening line.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="14" t="str">
-        <x:v>p90</x:v>
+        <x:v>p88</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>Professor Pixel</x:v>
@@ -3891,40 +3885,40 @@
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>s2_diagnosis_correct</x:v>
+        <x:v>scenarioStart_metacognition</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>proud</x:v>
+        <x:v>thinking</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>Exactly. Jordan used a strategy, but he cannot name it clearly or judge whether it helped. Before he can improve the process, he needs to make that process visible.</x:v>
+        <x:v>His performance improved. His strategy might have worked. But listen carefully to what Jordan actually knows about his learning.</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>p90.mp3</x:v>
+        <x:v>p88.mp3</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p90.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-02/p88.mp3</x:v>
       </x:c>
       <x:c r="I6" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J6" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K6" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L6" s="14"/>
       <x:c r="M6" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N6" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 opening line.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="14" t="str">
-        <x:v>p91</x:v>
+        <x:v>p89</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
         <x:v>Professor Pixel</x:v>
@@ -3933,40 +3927,40 @@
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>s2_diagnosis_transfer</x:v>
+        <x:v>scenarioStart_metacognition</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
         <x:v>encouraging</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
-        <x:v>Transfer matters, but Jordan first needs to identify and evaluate what happened during this task. Otherwise, his next plan is still a guess.</x:v>
+        <x:v>Let's figure out what's missing.</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>p91.mp3</x:v>
+        <x:v>p89.mp3</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p91.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-02/p89.mp3</x:v>
       </x:c>
       <x:c r="I7" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K7" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L7" s="14"/>
       <x:c r="M7" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N7" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 opening line.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="14" t="str">
-        <x:v>p92</x:v>
+        <x:v>p90</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
         <x:v>Professor Pixel</x:v>
@@ -3975,40 +3969,40 @@
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>s2_diagnosis_motivation</x:v>
+        <x:v>s2_diagnosis_correct</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>skeptical</x:v>
+        <x:v>proud</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>Jordan completed the assignment and is actively trying to understand the result. His uncertainty is not evidence that he lacks motivation.</x:v>
+        <x:v>That's the hidden problem. Jordan has an outcome and a strategy, but no evidence connecting the two. He cannot judge what helped or use that judgment to make his next decision.</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>p92.mp3</x:v>
+        <x:v>p90.mp3</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p92.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-02/p90.mp3</x:v>
       </x:c>
       <x:c r="I8" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J8" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K8" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L8" s="14"/>
       <x:c r="M8" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N8" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 diagnosis feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="14" t="str">
-        <x:v>p93</x:v>
+        <x:v>p91</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
         <x:v>Professor Pixel</x:v>
@@ -4017,40 +4011,40 @@
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>s2_diagnosis_grade</x:v>
+        <x:v>s2_diagnosis_strategy</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
-        <x:v>neutral</x:v>
+        <x:v>thinking</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>Jordan already knows the outcome. What he cannot explain is the learning process that produced it.</x:v>
+        <x:v>Rereading may not be his best strategy, but replacing it does not solve the deeper problem. Jordan still needs a way to tell why a strategy worked or failed.</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>p93.mp3</x:v>
+        <x:v>p91.mp3</x:v>
       </x:c>
       <x:c r="H9" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p93.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-02/p91.mp3</x:v>
       </x:c>
       <x:c r="I9" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J9" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K9" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L9" s="14"/>
       <x:c r="M9" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N9" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 diagnosis feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="14" t="str">
-        <x:v>p94</x:v>
+        <x:v>p92</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
         <x:v>Professor Pixel</x:v>
@@ -4059,82 +4053,82 @@
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>s2_diagnosis_evidence</x:v>
+        <x:v>s2_diagnosis_motivation</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>thinking</x:v>
+        <x:v>skeptical</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>Nothing Jordan said clearly points to time or task difficulty. Stay with the evidence rather than adding details the student did not provide.</x:v>
+        <x:v>Jordan completed the work and is trying to understand the result. The evidence points somewhere other than motivation.</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>p94.mp3</x:v>
+        <x:v>p92.mp3</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-02/p94.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-02/p92.mp3</x:v>
       </x:c>
       <x:c r="I10" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J10" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K10" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L10" s="14"/>
       <x:c r="M10" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N10" s="14" t="str">
-        <x:v>Dialogue is not final until the S2 opening is tested.</x:v>
+        <x:v>Current V429 diagnosis feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>jordan-s2-01</x:v>
+        <x:v>p93</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>Jordan</x:v>
+        <x:v>Professor Pixel</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>scenarioStart_metacognition</x:v>
+        <x:v>s2_diagnosis_performance</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
         <x:v>neutral</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>I got an 84 on this assignment. That’s better than last time, so I guess something worked.</x:v>
+        <x:v>The grade tells us how Jordan performed. It does not tell Jordan what produced the learning or what he should do next.</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>jordan-s2-01.mp3</x:v>
+        <x:v>p93.mp3</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
-        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-01.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-02/p93.mp3</x:v>
       </x:c>
       <x:c r="I11" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J11" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K11" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L11" s="14"/>
       <x:c r="M11" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N11" s="14" t="str">
-        <x:v>Jordan uses he/him pronouns. Dialogue remains editable.</x:v>
+        <x:v>Current V429 diagnosis feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="14" t="str">
-        <x:v>jordan-s2-02</x:v>
+        <x:v>jordan-s2-intervention-confidence</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
         <x:v>Jordan</x:v>
@@ -4143,40 +4137,40 @@
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>scenarioStart_metacognition</x:v>
+        <x:v>S2 intervention</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>uncertain</x:v>
+        <x:v>confident</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>I reread the chapter a few times. Some parts finally made more sense, but I couldn’t tell you what actually helped.</x:v>
+        <x:v>I'd say I'm a four out of five. I feel better about it this time.</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>jordan-s2-02.mp3</x:v>
+        <x:v>jordan-s2-intervention-confidence.mp3</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str">
-        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-02.mp3</x:v>
+        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-confidence.mp3</x:v>
       </x:c>
       <x:c r="I12" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J12" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K12" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L12" s="14"/>
       <x:c r="M12" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N12" s="14" t="str">
-        <x:v>Jordan uses he/him pronouns. Dialogue remains editable.</x:v>
+        <x:v>Current V429 intervention response.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="14" t="str">
-        <x:v>jordan-s2-03</x:v>
+        <x:v>jordan-s2-intervention-strategy</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
         <x:v>Jordan</x:v>
@@ -4185,35 +4179,119 @@
         <x:v>Scenario 2</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>scenarioStart_metacognition</x:v>
+        <x:v>S2 intervention</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>frustrated</x:v>
+        <x:v>thinking</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>When the next assignment starts, I’ll probably reread everything again and hope it works. That is more or less my entire academic strategy.</x:v>
+        <x:v>I reread the chapter three times and highlighted the parts that seemed important.</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>jordan-s2-03.mp3</x:v>
+        <x:v>jordan-s2-intervention-strategy.mp3</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str">
-        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-03.mp3</x:v>
+        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-strategy.mp3</x:v>
       </x:c>
       <x:c r="I13" s="14" t="str">
-        <x:v>Draft / rewrite before recording</x:v>
+        <x:v>Review before recording</x:v>
       </x:c>
       <x:c r="J13" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K13" s="14" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L13" s="14"/>
       <x:c r="M13" s="14" t="str">
-        <x:v>Planned S2</x:v>
+        <x:v>Active text / planned audio</x:v>
       </x:c>
       <x:c r="N13" s="14" t="str">
-        <x:v>Jordan uses he/him pronouns. Dialogue remains editable.</x:v>
+        <x:v>Current V429 intervention response.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>jordan-s2-intervention-grade</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Jordan</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Scenario 2</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>S2 intervention</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>confident</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>I got an 84 instead of a 76, so rereading must have worked.</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>jordan-s2-intervention-grade.mp3</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-grade.mp3</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>Review before recording</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="L14"/>
+      <x:c r="M14" t="str">
+        <x:v>Active text / planned audio</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>Current V429 intervention response.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>jordan-s2-intervention-evidence</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Jordan</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Scenario 2</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>S2 intervention</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>I could define both concepts, but without my notes I still couldn't explain the difference. Rereading helped me recognize them, but it didn't help me compare them. I need to try examples next.</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>jordan-s2-intervention-evidence.mp3</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-evidence.mp3</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>Review before recording</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="L15"/>
+      <x:c r="M15" t="str">
+        <x:v>Active text / planned audio</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>Current V429 intervention response.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4252,7 +4330,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R030560889a6641a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc839f70d17634703"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5941,7 +6019,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3107b231cfc64f13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19d009b8f86d462f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5960,20 +6038,24 @@
       </x:c>
       <x:c r="B1" s="63"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+    </x:row>
     <x:row r="3">
       <x:c r="A3" s="67" t="str">
         <x:v>Workbook purpose</x:v>
       </x:c>
       <x:c r="B3" s="73" t="str">
-        <x:v>A recording and dialogue-review workbook for the current PromptCraft v137 build.</x:v>
+        <x:v>Recording and dialogue-review workbook for the current PROMPTCRAFT_V429 build.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="67" t="str">
-        <x:v>Why it changed</x:v>
+        <x:v>Current source</x:v>
       </x:c>
       <x:c r="B4" s="73" t="str">
-        <x:v>The previous workbook still used numeric scenarioStart_0 through scenarioStart_7 keys, treated retired S2–S8 lines as active, and did not include the organized audio paths.</x:v>
+        <x:v>src/js/content/dialogue-data.js contains structured shared/S1/S2 dialogue; src/js/scenarios/s2-metacognition.js owns Jordan intervention fallback dialogue.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5981,7 +6063,7 @@
         <x:v>Active S1 + Shared</x:v>
       </x:c>
       <x:c r="B5" s="73" t="str">
-        <x:v>Use this sheet for current Professor Pixel recordings and S1 dialogue review.</x:v>
+        <x:v>Use for current Professor Pixel/shared recordings and S1 dialogue review.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5989,7 +6071,7 @@
         <x:v>S2 Draft</x:v>
       </x:c>
       <x:c r="B6" s="73" t="str">
-        <x:v>Contains p86–p94 for Professor Pixel and jordan-s2-01 through jordan-s2-03 for Jordan. These lines are provisional.</x:v>
+        <x:v>Despite the historical tab name, this sheet now lists current S2 opening/diagnosis text and active intervention voice IDs. Audio files remain planned until recorded.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5997,15 +6079,15 @@
         <x:v>Archived Dialogue</x:v>
       </x:c>
       <x:c r="B7" s="73" t="str">
-        <x:v>Preserves the prior S2–S8 script so useful wording can be recovered without reconnecting old mechanics.</x:v>
+        <x:v>Historical S2-S8 wording only. It may inspire new writing, but it must not be used to restore old scenario mechanics.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="67" t="str">
-        <x:v>Audio path convention</x:v>
+        <x:v>Audio paths</x:v>
       </x:c>
       <x:c r="B8" s="73" t="str">
-        <x:v>Professor Pixel lines use assets/audio/voice/professor-pixel/... and student lines use assets/audio/voice/students/&lt;name&gt;/scenario-##/.</x:v>
+        <x:v>Professor Pixel lines use assets/audio/voice/professor-pixel/...; student lines use assets/audio/voice/students/&lt;name&gt;/scenario-##/.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6013,23 +6095,23 @@
         <x:v>Recording workflow</x:v>
       </x:c>
       <x:c r="B9" s="73" t="str">
-        <x:v>Review Dialogue line and Recording recommendation, record to the listed Full audio path, then update Production status and Needs re-record?.</x:v>
+        <x:v>Review current code text, record to the listed Full audio path, then update Production status and Needs re-record?.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="67" t="str">
-        <x:v>Dynamic lines</x:v>
+        <x:v>Dynamic/text-only lines</x:v>
       </x:c>
       <x:c r="B10" s="73" t="str">
-        <x:v>Lines with names, counts, or inserted missing items should be rewritten into a generic recordable version or left text-only.</x:v>
+        <x:v>Names, inserted values, generated analysis, and other dynamic content should stay text/TTS unless a generic recordable version is intentionally designed.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="67" t="str">
-        <x:v>Source of truth</x:v>
+        <x:v>Compatibility note</x:v>
       </x:c>
       <x:c r="B11" s="73" t="str">
-        <x:v>The current functions/dialogue.js and functions/app.js determine what is actually loaded by the app.</x:v>
+        <x:v>The app remains PROMPTCRAFT_V429 / schema V121 / receiver V82. Cache revision 446 is not a new app build.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
